--- a/pricing/input/routes-live/video-enabled.xlsx
+++ b/pricing/input/routes-live/video-enabled.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="223">
   <si>
     <t>模型编码</t>
   </si>
@@ -50,6 +50,171 @@
     <t>官方价/线路成本</t>
   </si>
   <si>
+    <t>doubao-seedance-2-0-260128</t>
+  </si>
+  <si>
+    <t>Seedance 2.0</t>
+  </si>
+  <si>
+    <t>Seedance CN</t>
+  </si>
+  <si>
+    <t>seedance_cn-doubao-seedance-2-0-260128</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>video_token | 官方 2.3881 / 成本 2.3881</t>
+  </si>
+  <si>
+    <t>video_token | 官方 3.8806 / 成本 3.8806</t>
+  </si>
+  <si>
+    <t>video_token | 官方 4.6269 / 成本 4.6269</t>
+  </si>
+  <si>
+    <t>video_token | 官方 7.612 / 成本 7.612</t>
+  </si>
+  <si>
+    <t>video_token | 官方 4.1792 / 成本 4.1792</t>
+  </si>
+  <si>
+    <t>video_token | 官方 6.8657 / 成本 6.8657</t>
+  </si>
+  <si>
+    <t>doubao-seedance-2-0-fast-260128</t>
+  </si>
+  <si>
+    <t>Seedance 2.0 Fast</t>
+  </si>
+  <si>
+    <t>seedance_cn-doubao-seedance-2-0-fast-260128</t>
+  </si>
+  <si>
+    <t>video_token | 官方 3.2836 / 成本 3.2836</t>
+  </si>
+  <si>
+    <t>video_token | 官方 5.5224 / 成本 5.5224</t>
+  </si>
+  <si>
+    <t>doubao-seedance-2-0-mini-260615</t>
+  </si>
+  <si>
+    <t>Seedance 2.0 Mini</t>
+  </si>
+  <si>
+    <t>seedance_cn-doubao-seedance-2-0-mini-260615</t>
+  </si>
+  <si>
+    <t>video_token | 官方 2.0896 / 成本 2.0896</t>
+  </si>
+  <si>
+    <t>video_token | 官方 3.4329 / 成本 3.4329</t>
+  </si>
+  <si>
+    <t>doubao-seedance-2-5-260628</t>
+  </si>
+  <si>
+    <t>Seedance 2.5</t>
+  </si>
+  <si>
+    <t>seedance_cn-doubao-seedance-2-5-260628</t>
+  </si>
+  <si>
+    <t>video_token | 官方 11.4926 / 成本 11.4926</t>
+  </si>
+  <si>
+    <t>video_token | 官方 6.2687 / 成本 6.2687</t>
+  </si>
+  <si>
+    <t>video_token | 官方 10.4478 / 成本 10.4478</t>
+  </si>
+  <si>
+    <t>dreamina-seedance-2-0-260128</t>
+  </si>
+  <si>
+    <t>Seedance Global</t>
+  </si>
+  <si>
+    <t>seedance_glo-dreamina-seedance-2-0-260128</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>video_token | 官方 2.4 / 成本 2.4</t>
+  </si>
+  <si>
+    <t>video_token | 官方 4 / 成本 4</t>
+  </si>
+  <si>
+    <t>video_token | 官方 4.7 / 成本 4.7</t>
+  </si>
+  <si>
+    <t>video_token | 官方 7.7 / 成本 7.7</t>
+  </si>
+  <si>
+    <t>video_token | 官方 4.3 / 成本 4.3</t>
+  </si>
+  <si>
+    <t>video_token | 官方 7 / 成本 7</t>
+  </si>
+  <si>
+    <t>dreamina-seedance-2-0-fast-260128</t>
+  </si>
+  <si>
+    <t>seedance_glo-dreamina-seedance-2-0-fast-260128</t>
+  </si>
+  <si>
+    <t>video_token | 官方 3.3 / 成本 3.3</t>
+  </si>
+  <si>
+    <t>video_token | 官方 5.6 / 成本 5.6</t>
+  </si>
+  <si>
+    <t>dreamina-seedance-2-0-mini-260615</t>
+  </si>
+  <si>
+    <t>seedance_glo-dreamina-seedance-2-0-mini-260615</t>
+  </si>
+  <si>
+    <t>video_token | 官方 2.1 / 成本 2.1</t>
+  </si>
+  <si>
+    <t>video_token | 官方 3.5 / 成本 3.5</t>
+  </si>
+  <si>
+    <t>dreamina-seedance-2-5-260628</t>
+  </si>
+  <si>
+    <t>seedance_glo-dreamina-seedance-2-5-260628</t>
+  </si>
+  <si>
+    <t>video_token | 官方 11.7 / 成本 11.7</t>
+  </si>
+  <si>
+    <t>video_token | 官方 6.4 / 成本 6.4</t>
+  </si>
+  <si>
+    <t>video_token | 官方 10.7 / 成本 10.7</t>
+  </si>
+  <si>
     <t>gemini-omni-flash-preview</t>
   </si>
   <si>
@@ -65,21 +230,9 @@
     <t>P0</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>7.5折</t>
   </si>
   <si>
-    <t>正常</t>
-  </si>
-  <si>
-    <t>启用</t>
-  </si>
-  <si>
     <t>video_token · output_video | 官方 17.5 / 成本 13.125</t>
   </si>
   <si>
@@ -101,9 +254,6 @@
     <t>OpenSand-Grok-Imagine-Video-1.5</t>
   </si>
   <si>
-    <t>P10</t>
-  </si>
-  <si>
     <t>3.2折</t>
   </si>
   <si>
@@ -260,9 +410,6 @@
     <t>seedance-2.0-os</t>
   </si>
   <si>
-    <t>Seedance 2.0</t>
-  </si>
-  <si>
     <t>OpenSand-国内</t>
   </si>
   <si>
@@ -359,9 +506,6 @@
     <t>vidu-海外-viduq2</t>
   </si>
   <si>
-    <t>P1</t>
-  </si>
-  <si>
     <t>5.5折</t>
   </si>
   <si>
@@ -498,9 +642,6 @@
   </si>
   <si>
     <t>百炼-Wan2.6-北京</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>video_second | 官方 0.15 / 成本 0.143353</t>
@@ -590,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="4.66796875" customWidth="true" bestFit="true"/>
@@ -761,168 +902,168 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="1">
         <v>25</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s" s="1">
-        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s" s="1">
         <v>26</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L6" t="s" s="1">
-        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L7" t="s" s="1">
-        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s" s="1">
         <v>26</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L8" t="s" s="1">
-        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s" s="2">
         <v>16</v>
@@ -937,7 +1078,7 @@
         <v>18</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s" s="2">
         <v>20</v>
@@ -946,21 +1087,21 @@
         <v>21</v>
       </c>
       <c r="L9" t="s" s="1">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s" s="2">
         <v>16</v>
@@ -975,7 +1116,7 @@
         <v>18</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
@@ -984,21 +1125,21 @@
         <v>21</v>
       </c>
       <c r="L10" t="s" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s" s="2">
         <v>16</v>
@@ -1013,7 +1154,7 @@
         <v>18</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
@@ -1022,21 +1163,21 @@
         <v>21</v>
       </c>
       <c r="L11" t="s" s="1">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s" s="2">
         <v>16</v>
@@ -1051,7 +1192,7 @@
         <v>18</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
@@ -1060,21 +1201,21 @@
         <v>21</v>
       </c>
       <c r="L12" t="s" s="1">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s" s="2">
         <v>16</v>
@@ -1089,7 +1230,7 @@
         <v>18</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>20</v>
@@ -1098,24 +1239,24 @@
         <v>21</v>
       </c>
       <c r="L13" t="s" s="1">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>17</v>
@@ -1127,7 +1268,7 @@
         <v>18</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>20</v>
@@ -1136,24 +1277,24 @@
         <v>21</v>
       </c>
       <c r="L14" t="s" s="1">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>17</v>
@@ -1165,7 +1306,7 @@
         <v>18</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>20</v>
@@ -1174,21 +1315,21 @@
         <v>21</v>
       </c>
       <c r="L15" t="s" s="1">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s" s="2">
         <v>16</v>
@@ -1203,7 +1344,7 @@
         <v>18</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>20</v>
@@ -1212,21 +1353,21 @@
         <v>21</v>
       </c>
       <c r="L16" t="s" s="1">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s" s="2">
         <v>16</v>
@@ -1241,7 +1382,7 @@
         <v>18</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>20</v>
@@ -1250,21 +1391,21 @@
         <v>21</v>
       </c>
       <c r="L17" t="s" s="1">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s" s="2">
         <v>16</v>
@@ -1279,7 +1420,7 @@
         <v>18</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>20</v>
@@ -1288,24 +1429,24 @@
         <v>21</v>
       </c>
       <c r="L18" t="s" s="1">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>17</v>
@@ -1317,7 +1458,7 @@
         <v>18</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>20</v>
@@ -1326,24 +1467,24 @@
         <v>21</v>
       </c>
       <c r="L19" t="s" s="1">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>17</v>
@@ -1355,7 +1496,7 @@
         <v>18</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>20</v>
@@ -1364,24 +1505,24 @@
         <v>21</v>
       </c>
       <c r="L20" t="s" s="1">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>17</v>
@@ -1393,7 +1534,7 @@
         <v>18</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>20</v>
@@ -1402,24 +1543,24 @@
         <v>21</v>
       </c>
       <c r="L21" t="s" s="1">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>17</v>
@@ -1431,7 +1572,7 @@
         <v>18</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>20</v>
@@ -1440,24 +1581,24 @@
         <v>21</v>
       </c>
       <c r="L22" t="s" s="1">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>17</v>
@@ -1469,7 +1610,7 @@
         <v>18</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>20</v>
@@ -1478,24 +1619,24 @@
         <v>21</v>
       </c>
       <c r="L23" t="s" s="1">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>17</v>
@@ -1507,7 +1648,7 @@
         <v>18</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>20</v>
@@ -1516,24 +1657,24 @@
         <v>21</v>
       </c>
       <c r="L24" t="s" s="1">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>17</v>
@@ -1545,7 +1686,7 @@
         <v>18</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>20</v>
@@ -1554,24 +1695,24 @@
         <v>21</v>
       </c>
       <c r="L25" t="s" s="1">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>17</v>
@@ -1583,7 +1724,7 @@
         <v>18</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>20</v>
@@ -1592,24 +1733,24 @@
         <v>21</v>
       </c>
       <c r="L26" t="s" s="1">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>17</v>
@@ -1621,7 +1762,7 @@
         <v>18</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>20</v>
@@ -1630,24 +1771,24 @@
         <v>21</v>
       </c>
       <c r="L27" t="s" s="1">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>17</v>
@@ -1659,7 +1800,7 @@
         <v>18</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>20</v>
@@ -1668,24 +1809,24 @@
         <v>21</v>
       </c>
       <c r="L28" t="s" s="1">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>17</v>
@@ -1697,7 +1838,7 @@
         <v>18</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>20</v>
@@ -1706,24 +1847,24 @@
         <v>21</v>
       </c>
       <c r="L29" t="s" s="1">
-        <v>79</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>17</v>
@@ -1735,7 +1876,7 @@
         <v>18</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>20</v>
@@ -1744,24 +1885,24 @@
         <v>21</v>
       </c>
       <c r="L30" t="s" s="1">
-        <v>79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>17</v>
@@ -1773,7 +1914,7 @@
         <v>18</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>20</v>
@@ -1782,24 +1923,24 @@
         <v>21</v>
       </c>
       <c r="L31" t="s" s="1">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>17</v>
@@ -1811,7 +1952,7 @@
         <v>18</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>20</v>
@@ -1820,24 +1961,24 @@
         <v>21</v>
       </c>
       <c r="L32" t="s" s="1">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>17</v>
@@ -1849,7 +1990,7 @@
         <v>18</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>20</v>
@@ -1858,24 +1999,24 @@
         <v>21</v>
       </c>
       <c r="L33" t="s" s="1">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>17</v>
@@ -1887,7 +2028,7 @@
         <v>18</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>20</v>
@@ -1896,24 +2037,24 @@
         <v>21</v>
       </c>
       <c r="L34" t="s" s="1">
-        <v>86</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>17</v>
@@ -1925,7 +2066,7 @@
         <v>18</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>20</v>
@@ -1934,24 +2075,24 @@
         <v>21</v>
       </c>
       <c r="L35" t="s" s="1">
-        <v>87</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>17</v>
@@ -1963,7 +2104,7 @@
         <v>18</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>20</v>
@@ -1972,24 +2113,24 @@
         <v>21</v>
       </c>
       <c r="L36" t="s" s="1">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>17</v>
@@ -2001,7 +2142,7 @@
         <v>18</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>20</v>
@@ -2010,24 +2151,24 @@
         <v>21</v>
       </c>
       <c r="L37" t="s" s="1">
-        <v>88</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>17</v>
@@ -2039,7 +2180,7 @@
         <v>18</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>20</v>
@@ -2048,24 +2189,24 @@
         <v>21</v>
       </c>
       <c r="L38" t="s" s="1">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>17</v>
@@ -2077,7 +2218,7 @@
         <v>18</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>20</v>
@@ -2086,21 +2227,21 @@
         <v>21</v>
       </c>
       <c r="L39" t="s" s="1">
-        <v>89</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s" s="2">
         <v>16</v>
@@ -2115,7 +2256,7 @@
         <v>18</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>20</v>
@@ -2124,21 +2265,21 @@
         <v>21</v>
       </c>
       <c r="L40" t="s" s="1">
-        <v>90</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s" s="2">
         <v>16</v>
@@ -2153,7 +2294,7 @@
         <v>18</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>20</v>
@@ -2162,21 +2303,21 @@
         <v>21</v>
       </c>
       <c r="L41" t="s" s="1">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E42" t="s" s="2">
         <v>16</v>
@@ -2191,30 +2332,30 @@
         <v>18</v>
       </c>
       <c r="I42" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L42" t="s" s="1">
         <v>65</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L42" t="s" s="1">
-        <v>86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s" s="2">
         <v>16</v>
@@ -2229,7 +2370,7 @@
         <v>18</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>20</v>
@@ -2238,21 +2379,21 @@
         <v>21</v>
       </c>
       <c r="L43" t="s" s="1">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E44" t="s" s="2">
         <v>16</v>
@@ -2267,30 +2408,30 @@
         <v>18</v>
       </c>
       <c r="I44" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L44" t="s" s="1">
         <v>65</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L44" t="s" s="1">
-        <v>87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s" s="2">
         <v>16</v>
@@ -2305,7 +2446,7 @@
         <v>18</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>20</v>
@@ -2314,24 +2455,24 @@
         <v>21</v>
       </c>
       <c r="L45" t="s" s="1">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>17</v>
@@ -2343,7 +2484,7 @@
         <v>18</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>20</v>
@@ -2352,24 +2493,24 @@
         <v>21</v>
       </c>
       <c r="L46" t="s" s="1">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>17</v>
@@ -2381,7 +2522,7 @@
         <v>18</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>20</v>
@@ -2390,24 +2531,24 @@
         <v>21</v>
       </c>
       <c r="L47" t="s" s="1">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>17</v>
@@ -2419,7 +2560,7 @@
         <v>18</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>20</v>
@@ -2428,24 +2569,24 @@
         <v>21</v>
       </c>
       <c r="L48" t="s" s="1">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>17</v>
@@ -2457,7 +2598,7 @@
         <v>18</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>20</v>
@@ -2466,24 +2607,24 @@
         <v>21</v>
       </c>
       <c r="L49" t="s" s="1">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>17</v>
@@ -2495,7 +2636,7 @@
         <v>18</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>20</v>
@@ -2504,24 +2645,24 @@
         <v>21</v>
       </c>
       <c r="L50" t="s" s="1">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>17</v>
@@ -2533,7 +2674,7 @@
         <v>18</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>20</v>
@@ -2542,24 +2683,24 @@
         <v>21</v>
       </c>
       <c r="L51" t="s" s="1">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>17</v>
@@ -2571,7 +2712,7 @@
         <v>18</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>20</v>
@@ -2580,24 +2721,24 @@
         <v>21</v>
       </c>
       <c r="L52" t="s" s="1">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>17</v>
@@ -2609,7 +2750,7 @@
         <v>18</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>20</v>
@@ -2618,24 +2759,24 @@
         <v>21</v>
       </c>
       <c r="L53" t="s" s="1">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>17</v>
@@ -2647,7 +2788,7 @@
         <v>18</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>20</v>
@@ -2656,24 +2797,24 @@
         <v>21</v>
       </c>
       <c r="L54" t="s" s="1">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>17</v>
@@ -2685,7 +2826,7 @@
         <v>18</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>20</v>
@@ -2694,62 +2835,62 @@
         <v>21</v>
       </c>
       <c r="L55" t="s" s="1">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L56" t="s" s="1">
         <v>96</v>
-      </c>
-      <c r="D56" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="E56" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="F56" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L56" t="s" s="1">
-        <v>110</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>17</v>
@@ -2761,7 +2902,7 @@
         <v>18</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>20</v>
@@ -2770,24 +2911,24 @@
         <v>21</v>
       </c>
       <c r="L57" t="s" s="1">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>17</v>
@@ -2799,7 +2940,7 @@
         <v>18</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>20</v>
@@ -2808,24 +2949,24 @@
         <v>21</v>
       </c>
       <c r="L58" t="s" s="1">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>17</v>
@@ -2837,7 +2978,7 @@
         <v>18</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>20</v>
@@ -2846,24 +2987,24 @@
         <v>21</v>
       </c>
       <c r="L59" t="s" s="1">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>17</v>
@@ -2875,7 +3016,7 @@
         <v>18</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>20</v>
@@ -2884,24 +3025,24 @@
         <v>21</v>
       </c>
       <c r="L60" t="s" s="1">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>17</v>
@@ -2913,7 +3054,7 @@
         <v>18</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>20</v>
@@ -2922,24 +3063,24 @@
         <v>21</v>
       </c>
       <c r="L61" t="s" s="1">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>17</v>
@@ -2951,7 +3092,7 @@
         <v>18</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>20</v>
@@ -2960,24 +3101,24 @@
         <v>21</v>
       </c>
       <c r="L62" t="s" s="1">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>17</v>
@@ -2989,7 +3130,7 @@
         <v>18</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>20</v>
@@ -2998,24 +3139,24 @@
         <v>21</v>
       </c>
       <c r="L63" t="s" s="1">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>17</v>
@@ -3027,7 +3168,7 @@
         <v>18</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>20</v>
@@ -3036,24 +3177,24 @@
         <v>21</v>
       </c>
       <c r="L64" t="s" s="1">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>17</v>
@@ -3065,7 +3206,7 @@
         <v>18</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>20</v>
@@ -3074,75 +3215,75 @@
         <v>21</v>
       </c>
       <c r="L65" t="s" s="1">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E66" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F66" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I66" t="s" s="2">
+      <c r="J66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L66" t="s" s="1">
         <v>116</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L66" t="s" s="1">
-        <v>127</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E67" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F67" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J67" t="s" s="2">
         <v>20</v>
       </c>
@@ -3150,37 +3291,37 @@
         <v>21</v>
       </c>
       <c r="L67" t="s" s="1">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E68" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I68" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F68" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J68" t="s" s="2">
         <v>20</v>
       </c>
@@ -3188,24 +3329,24 @@
         <v>21</v>
       </c>
       <c r="L68" t="s" s="1">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>17</v>
@@ -3217,7 +3358,7 @@
         <v>18</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>20</v>
@@ -3226,24 +3367,24 @@
         <v>21</v>
       </c>
       <c r="L69" t="s" s="1">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>17</v>
@@ -3255,7 +3396,7 @@
         <v>18</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>20</v>
@@ -3264,24 +3405,24 @@
         <v>21</v>
       </c>
       <c r="L70" t="s" s="1">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>17</v>
@@ -3293,7 +3434,7 @@
         <v>18</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>20</v>
@@ -3302,24 +3443,24 @@
         <v>21</v>
       </c>
       <c r="L71" t="s" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>17</v>
@@ -3331,7 +3472,7 @@
         <v>18</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>20</v>
@@ -3340,24 +3481,24 @@
         <v>21</v>
       </c>
       <c r="L72" t="s" s="1">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>17</v>
@@ -3369,7 +3510,7 @@
         <v>18</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>20</v>
@@ -3378,24 +3519,24 @@
         <v>21</v>
       </c>
       <c r="L73" t="s" s="1">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>17</v>
@@ -3407,7 +3548,7 @@
         <v>18</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>20</v>
@@ -3416,24 +3557,24 @@
         <v>21</v>
       </c>
       <c r="L74" t="s" s="1">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>17</v>
@@ -3445,7 +3586,7 @@
         <v>18</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>20</v>
@@ -3454,24 +3595,24 @@
         <v>21</v>
       </c>
       <c r="L75" t="s" s="1">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>17</v>
@@ -3483,7 +3624,7 @@
         <v>18</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>20</v>
@@ -3492,37 +3633,37 @@
         <v>21</v>
       </c>
       <c r="L76" t="s" s="1">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>146</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E77" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F77" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J77" t="s" s="2">
         <v>20</v>
       </c>
@@ -3530,37 +3671,37 @@
         <v>21</v>
       </c>
       <c r="L77" t="s" s="1">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>146</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E78" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I78" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F78" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J78" t="s" s="2">
         <v>20</v>
       </c>
@@ -3568,37 +3709,37 @@
         <v>21</v>
       </c>
       <c r="L78" t="s" s="1">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>146</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E79" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I79" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F79" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J79" t="s" s="2">
         <v>20</v>
       </c>
@@ -3606,37 +3747,37 @@
         <v>21</v>
       </c>
       <c r="L79" t="s" s="1">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E80" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I80" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F80" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J80" t="s" s="2">
         <v>20</v>
       </c>
@@ -3644,37 +3785,37 @@
         <v>21</v>
       </c>
       <c r="L80" t="s" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="E81" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I81" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F81" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J81" t="s" s="2">
         <v>20</v>
       </c>
@@ -3682,37 +3823,37 @@
         <v>21</v>
       </c>
       <c r="L81" t="s" s="1">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="E82" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I82" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F82" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J82" t="s" s="2">
         <v>20</v>
       </c>
@@ -3720,37 +3861,37 @@
         <v>21</v>
       </c>
       <c r="L82" t="s" s="1">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="E83" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I83" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F83" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J83" t="s" s="2">
         <v>20</v>
       </c>
@@ -3758,37 +3899,37 @@
         <v>21</v>
       </c>
       <c r="L83" t="s" s="1">
-        <v>156</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="E84" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I84" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F84" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J84" t="s" s="2">
         <v>20</v>
       </c>
@@ -3796,37 +3937,37 @@
         <v>21</v>
       </c>
       <c r="L84" t="s" s="1">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="E85" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I85" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F85" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J85" t="s" s="2">
         <v>20</v>
       </c>
@@ -3834,37 +3975,37 @@
         <v>21</v>
       </c>
       <c r="L85" t="s" s="1">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="E86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I86" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F86" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J86" t="s" s="2">
         <v>20</v>
       </c>
@@ -3872,37 +4013,37 @@
         <v>21</v>
       </c>
       <c r="L86" t="s" s="1">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="E87" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I87" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="F87" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="J87" t="s" s="2">
         <v>20</v>
       </c>
@@ -3910,24 +4051,24 @@
         <v>21</v>
       </c>
       <c r="L87" t="s" s="1">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>17</v>
@@ -3939,7 +4080,7 @@
         <v>18</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>20</v>
@@ -3948,24 +4089,24 @@
         <v>21</v>
       </c>
       <c r="L88" t="s" s="1">
-        <v>163</v>
+        <v>136</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>17</v>
@@ -3977,7 +4118,7 @@
         <v>18</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>20</v>
@@ -3986,24 +4127,24 @@
         <v>21</v>
       </c>
       <c r="L89" t="s" s="1">
-        <v>164</v>
+        <v>136</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>17</v>
@@ -4015,7 +4156,7 @@
         <v>18</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>20</v>
@@ -4024,24 +4165,24 @@
         <v>21</v>
       </c>
       <c r="L90" t="s" s="1">
-        <v>168</v>
+        <v>137</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>17</v>
@@ -4053,7 +4194,7 @@
         <v>18</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>20</v>
@@ -4062,24 +4203,24 @@
         <v>21</v>
       </c>
       <c r="L91" t="s" s="1">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>17</v>
@@ -4091,7 +4232,7 @@
         <v>18</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>20</v>
@@ -4100,24 +4241,24 @@
         <v>21</v>
       </c>
       <c r="L92" t="s" s="1">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>17</v>
@@ -4129,7 +4270,7 @@
         <v>18</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>20</v>
@@ -4138,24 +4279,24 @@
         <v>21</v>
       </c>
       <c r="L93" t="s" s="1">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>17</v>
@@ -4167,7 +4308,7 @@
         <v>18</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>20</v>
@@ -4176,346 +4317,2106 @@
         <v>21</v>
       </c>
       <c r="L94" t="s" s="1">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L95" t="s" s="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L96" t="s" s="1">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E97" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F97" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L97" t="s" s="1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E98" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F98" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L98" t="s" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F99" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L99" t="s" s="1">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F100" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L100" t="s" s="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F101" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L101" t="s" s="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L102" t="s" s="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L103" t="s" s="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F104" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L104" t="s" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F105" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L105" t="s" s="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E106" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F106" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L106" t="s" s="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E107" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F107" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L107" t="s" s="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E108" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F108" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L108" t="s" s="1">
         <v>173</v>
       </c>
-      <c r="B95" t="s" s="2">
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E109" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F109" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L109" t="s" s="1">
         <v>174</v>
       </c>
-      <c r="C95" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="D95" t="s" s="2">
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L110" t="s" s="1">
         <v>175</v>
       </c>
-      <c r="E95" t="s" s="2">
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E111" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="F95" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I95" t="s" s="2">
+      <c r="F111" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L111" t="s" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C112" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="J95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="L95" t="s" s="1">
+      <c r="D112" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I112" t="s" s="2">
         <v>164</v>
       </c>
+      <c r="J112" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L112" t="s" s="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L113" t="s" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D114" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E114" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L114" t="s" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="E115" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L115" t="s" s="1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E116" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F116" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L116" t="s" s="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F117" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L117" t="s" s="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F118" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L118" t="s" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F119" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L119" t="s" s="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="E120" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F120" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L120" t="s" s="1">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="E121" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F121" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L121" t="s" s="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D122" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="E122" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F122" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L122" t="s" s="1">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="E123" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F123" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L123" t="s" s="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="E124" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F124" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L124" t="s" s="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D125" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="E125" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F125" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L125" t="s" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E126" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F126" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L126" t="s" s="1">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D127" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E127" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F127" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L127" t="s" s="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D128" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E128" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F128" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L128" t="s" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D129" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F129" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L129" t="s" s="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D130" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F130" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L130" t="s" s="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="D131" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="E131" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="F131" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L131" t="s" s="1">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="E132" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F132" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L132" t="s" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="E133" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F133" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L133" t="s" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="E134" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F134" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L134" t="s" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D135" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="E135" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F135" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L135" t="s" s="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D136" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="E136" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F136" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L136" t="s" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D137" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="E137" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F137" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L137" t="s" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E138" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F138" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L138" t="s" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="D139" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E139" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F139" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L139" t="s" s="1">
+        <v>211</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="297">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K5:K8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="K22:K24"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="E25:E28"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="G25:G28"/>
-    <mergeCell ref="H25:H28"/>
-    <mergeCell ref="I25:I28"/>
-    <mergeCell ref="J25:J28"/>
-    <mergeCell ref="K25:K28"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="E29:E32"/>
-    <mergeCell ref="F29:F32"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="H29:H32"/>
-    <mergeCell ref="I29:I32"/>
-    <mergeCell ref="J29:J32"/>
-    <mergeCell ref="K29:K32"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="B33:B40"/>
-    <mergeCell ref="C33:C40"/>
-    <mergeCell ref="D33:D40"/>
-    <mergeCell ref="E33:E40"/>
-    <mergeCell ref="F33:F40"/>
-    <mergeCell ref="G33:G40"/>
-    <mergeCell ref="H33:H40"/>
-    <mergeCell ref="I33:I40"/>
-    <mergeCell ref="J33:J40"/>
-    <mergeCell ref="K33:K40"/>
-    <mergeCell ref="A41:A48"/>
-    <mergeCell ref="B41:B48"/>
-    <mergeCell ref="C41:C48"/>
-    <mergeCell ref="D41:D48"/>
-    <mergeCell ref="E41:E48"/>
-    <mergeCell ref="F41:F48"/>
-    <mergeCell ref="G41:G48"/>
-    <mergeCell ref="H41:H48"/>
-    <mergeCell ref="I41:I48"/>
-    <mergeCell ref="J41:J48"/>
-    <mergeCell ref="K41:K48"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="E49:E51"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="H49:H51"/>
-    <mergeCell ref="I49:I51"/>
-    <mergeCell ref="J49:J51"/>
-    <mergeCell ref="K49:K51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="H52:H54"/>
-    <mergeCell ref="I52:I54"/>
-    <mergeCell ref="J52:J54"/>
-    <mergeCell ref="K52:K54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="A57:A62"/>
-    <mergeCell ref="B57:B62"/>
-    <mergeCell ref="C57:C62"/>
-    <mergeCell ref="D57:D62"/>
-    <mergeCell ref="E57:E62"/>
-    <mergeCell ref="F57:F62"/>
-    <mergeCell ref="G57:G62"/>
-    <mergeCell ref="H57:H62"/>
-    <mergeCell ref="I57:I62"/>
-    <mergeCell ref="J57:J62"/>
-    <mergeCell ref="K57:K62"/>
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="C63:C68"/>
-    <mergeCell ref="D63:D68"/>
-    <mergeCell ref="E63:E68"/>
-    <mergeCell ref="F63:F68"/>
-    <mergeCell ref="G63:G68"/>
-    <mergeCell ref="H63:H68"/>
-    <mergeCell ref="I63:I68"/>
-    <mergeCell ref="J63:J68"/>
-    <mergeCell ref="K63:K68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="E69:E71"/>
-    <mergeCell ref="F69:F71"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="J69:J71"/>
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="C72:C74"/>
-    <mergeCell ref="D72:D74"/>
-    <mergeCell ref="E72:E74"/>
-    <mergeCell ref="F72:F74"/>
-    <mergeCell ref="G72:G74"/>
-    <mergeCell ref="H72:H74"/>
-    <mergeCell ref="I72:I74"/>
-    <mergeCell ref="J72:J74"/>
-    <mergeCell ref="K72:K74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="J75:J76"/>
-    <mergeCell ref="K75:K76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="F77:F79"/>
-    <mergeCell ref="G77:G79"/>
-    <mergeCell ref="H77:H79"/>
-    <mergeCell ref="I77:I79"/>
-    <mergeCell ref="J77:J79"/>
-    <mergeCell ref="K77:K79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="K80:K81"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="B82:B87"/>
-    <mergeCell ref="C82:C87"/>
-    <mergeCell ref="D82:D87"/>
-    <mergeCell ref="E82:E87"/>
-    <mergeCell ref="F82:F87"/>
-    <mergeCell ref="G82:G87"/>
-    <mergeCell ref="H82:H87"/>
-    <mergeCell ref="I82:I87"/>
-    <mergeCell ref="J82:J87"/>
-    <mergeCell ref="K82:K87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="D88:D89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="H88:H89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="J88:J89"/>
-    <mergeCell ref="K88:K89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:F91"/>
-    <mergeCell ref="G90:G91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="J90:J91"/>
-    <mergeCell ref="K90:K91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="F92:F93"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="H92:H93"/>
-    <mergeCell ref="I92:I93"/>
-    <mergeCell ref="J92:J93"/>
-    <mergeCell ref="K92:K93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="H94:H95"/>
-    <mergeCell ref="I94:I95"/>
-    <mergeCell ref="J94:J95"/>
-    <mergeCell ref="K94:K95"/>
+  <mergeCells count="385">
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="C2:C9"/>
+    <mergeCell ref="D2:D9"/>
+    <mergeCell ref="E2:E9"/>
+    <mergeCell ref="F2:F9"/>
+    <mergeCell ref="G2:G9"/>
+    <mergeCell ref="H2:H9"/>
+    <mergeCell ref="I2:I9"/>
+    <mergeCell ref="J2:J9"/>
+    <mergeCell ref="K2:K9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="I10:I13"/>
+    <mergeCell ref="J10:J13"/>
+    <mergeCell ref="K10:K13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="I14:I17"/>
+    <mergeCell ref="J14:J17"/>
+    <mergeCell ref="K14:K17"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="C18:C23"/>
+    <mergeCell ref="D18:D23"/>
+    <mergeCell ref="E18:E23"/>
+    <mergeCell ref="F18:F23"/>
+    <mergeCell ref="G18:G23"/>
+    <mergeCell ref="H18:H23"/>
+    <mergeCell ref="I18:I23"/>
+    <mergeCell ref="J18:J23"/>
+    <mergeCell ref="K18:K23"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="C24:C31"/>
+    <mergeCell ref="D24:D31"/>
+    <mergeCell ref="E24:E31"/>
+    <mergeCell ref="F24:F31"/>
+    <mergeCell ref="G24:G31"/>
+    <mergeCell ref="H24:H31"/>
+    <mergeCell ref="I24:I31"/>
+    <mergeCell ref="J24:J31"/>
+    <mergeCell ref="K24:K31"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="D32:D35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="H32:H35"/>
+    <mergeCell ref="I32:I35"/>
+    <mergeCell ref="J32:J35"/>
+    <mergeCell ref="K32:K35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="F36:F39"/>
+    <mergeCell ref="G36:G39"/>
+    <mergeCell ref="H36:H39"/>
+    <mergeCell ref="I36:I39"/>
+    <mergeCell ref="J36:J39"/>
+    <mergeCell ref="K36:K39"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="D40:D45"/>
+    <mergeCell ref="E40:E45"/>
+    <mergeCell ref="F40:F45"/>
+    <mergeCell ref="G40:G45"/>
+    <mergeCell ref="H40:H45"/>
+    <mergeCell ref="I40:I45"/>
+    <mergeCell ref="J40:J45"/>
+    <mergeCell ref="K40:K45"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="F46:F48"/>
+    <mergeCell ref="G46:G48"/>
+    <mergeCell ref="H46:H48"/>
+    <mergeCell ref="I46:I48"/>
+    <mergeCell ref="J46:J48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="E49:E52"/>
+    <mergeCell ref="F49:F52"/>
+    <mergeCell ref="G49:G52"/>
+    <mergeCell ref="H49:H52"/>
+    <mergeCell ref="I49:I52"/>
+    <mergeCell ref="J49:J52"/>
+    <mergeCell ref="K49:K52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="F53:F55"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="I53:I55"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="K53:K55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F60:F62"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="E63:E65"/>
+    <mergeCell ref="F63:F65"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="H63:H65"/>
+    <mergeCell ref="I63:I65"/>
+    <mergeCell ref="J63:J65"/>
+    <mergeCell ref="K63:K65"/>
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="D66:D68"/>
+    <mergeCell ref="E66:E68"/>
+    <mergeCell ref="F66:F68"/>
+    <mergeCell ref="G66:G68"/>
+    <mergeCell ref="H66:H68"/>
+    <mergeCell ref="I66:I68"/>
+    <mergeCell ref="J66:J68"/>
+    <mergeCell ref="K66:K68"/>
+    <mergeCell ref="A69:A72"/>
+    <mergeCell ref="B69:B72"/>
+    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="D69:D72"/>
+    <mergeCell ref="E69:E72"/>
+    <mergeCell ref="F69:F72"/>
+    <mergeCell ref="G69:G72"/>
+    <mergeCell ref="H69:H72"/>
+    <mergeCell ref="I69:I72"/>
+    <mergeCell ref="J69:J72"/>
+    <mergeCell ref="K69:K72"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="B73:B76"/>
+    <mergeCell ref="C73:C76"/>
+    <mergeCell ref="D73:D76"/>
+    <mergeCell ref="E73:E76"/>
+    <mergeCell ref="F73:F76"/>
+    <mergeCell ref="G73:G76"/>
+    <mergeCell ref="H73:H76"/>
+    <mergeCell ref="I73:I76"/>
+    <mergeCell ref="J73:J76"/>
+    <mergeCell ref="K73:K76"/>
+    <mergeCell ref="A77:A84"/>
+    <mergeCell ref="B77:B84"/>
+    <mergeCell ref="C77:C84"/>
+    <mergeCell ref="D77:D84"/>
+    <mergeCell ref="E77:E84"/>
+    <mergeCell ref="F77:F84"/>
+    <mergeCell ref="G77:G84"/>
+    <mergeCell ref="H77:H84"/>
+    <mergeCell ref="I77:I84"/>
+    <mergeCell ref="J77:J84"/>
+    <mergeCell ref="K77:K84"/>
+    <mergeCell ref="A85:A92"/>
+    <mergeCell ref="B85:B92"/>
+    <mergeCell ref="C85:C92"/>
+    <mergeCell ref="D85:D92"/>
+    <mergeCell ref="E85:E92"/>
+    <mergeCell ref="F85:F92"/>
+    <mergeCell ref="G85:G92"/>
+    <mergeCell ref="H85:H92"/>
+    <mergeCell ref="I85:I92"/>
+    <mergeCell ref="J85:J92"/>
+    <mergeCell ref="K85:K92"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="D93:D95"/>
+    <mergeCell ref="E93:E95"/>
+    <mergeCell ref="F93:F95"/>
+    <mergeCell ref="G93:G95"/>
+    <mergeCell ref="H93:H95"/>
+    <mergeCell ref="I93:I95"/>
+    <mergeCell ref="J93:J95"/>
+    <mergeCell ref="K93:K95"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="C96:C98"/>
+    <mergeCell ref="D96:D98"/>
+    <mergeCell ref="E96:E98"/>
+    <mergeCell ref="F96:F98"/>
+    <mergeCell ref="G96:G98"/>
+    <mergeCell ref="H96:H98"/>
+    <mergeCell ref="I96:I98"/>
+    <mergeCell ref="J96:J98"/>
+    <mergeCell ref="K96:K98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="E99:E100"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="K99:K100"/>
+    <mergeCell ref="A101:A106"/>
+    <mergeCell ref="B101:B106"/>
+    <mergeCell ref="C101:C106"/>
+    <mergeCell ref="D101:D106"/>
+    <mergeCell ref="E101:E106"/>
+    <mergeCell ref="F101:F106"/>
+    <mergeCell ref="G101:G106"/>
+    <mergeCell ref="H101:H106"/>
+    <mergeCell ref="I101:I106"/>
+    <mergeCell ref="J101:J106"/>
+    <mergeCell ref="K101:K106"/>
+    <mergeCell ref="A107:A112"/>
+    <mergeCell ref="B107:B112"/>
+    <mergeCell ref="C107:C112"/>
+    <mergeCell ref="D107:D112"/>
+    <mergeCell ref="E107:E112"/>
+    <mergeCell ref="F107:F112"/>
+    <mergeCell ref="G107:G112"/>
+    <mergeCell ref="H107:H112"/>
+    <mergeCell ref="I107:I112"/>
+    <mergeCell ref="J107:J112"/>
+    <mergeCell ref="K107:K112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:D115"/>
+    <mergeCell ref="E113:E115"/>
+    <mergeCell ref="F113:F115"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="H113:H115"/>
+    <mergeCell ref="I113:I115"/>
+    <mergeCell ref="J113:J115"/>
+    <mergeCell ref="K113:K115"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="E116:E118"/>
+    <mergeCell ref="F116:F118"/>
+    <mergeCell ref="G116:G118"/>
+    <mergeCell ref="H116:H118"/>
+    <mergeCell ref="I116:I118"/>
+    <mergeCell ref="J116:J118"/>
+    <mergeCell ref="K116:K118"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="E119:E120"/>
+    <mergeCell ref="F119:F120"/>
+    <mergeCell ref="G119:G120"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="J119:J120"/>
+    <mergeCell ref="K119:K120"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D121:D123"/>
+    <mergeCell ref="E121:E123"/>
+    <mergeCell ref="F121:F123"/>
+    <mergeCell ref="G121:G123"/>
+    <mergeCell ref="H121:H123"/>
+    <mergeCell ref="I121:I123"/>
+    <mergeCell ref="J121:J123"/>
+    <mergeCell ref="K121:K123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="I124:I125"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="K124:K125"/>
+    <mergeCell ref="A126:A131"/>
+    <mergeCell ref="B126:B131"/>
+    <mergeCell ref="C126:C131"/>
+    <mergeCell ref="D126:D131"/>
+    <mergeCell ref="E126:E131"/>
+    <mergeCell ref="F126:F131"/>
+    <mergeCell ref="G126:G131"/>
+    <mergeCell ref="H126:H131"/>
+    <mergeCell ref="I126:I131"/>
+    <mergeCell ref="J126:J131"/>
+    <mergeCell ref="K126:K131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="B132:B133"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
+    <mergeCell ref="E132:E133"/>
+    <mergeCell ref="F132:F133"/>
+    <mergeCell ref="G132:G133"/>
+    <mergeCell ref="H132:H133"/>
+    <mergeCell ref="I132:I133"/>
+    <mergeCell ref="J132:J133"/>
+    <mergeCell ref="K132:K133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="F134:F135"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="H134:H135"/>
+    <mergeCell ref="I134:I135"/>
+    <mergeCell ref="J134:J135"/>
+    <mergeCell ref="K134:K135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="H136:H137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="J136:J137"/>
+    <mergeCell ref="K136:K137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="K138:K139"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
